--- a/data/STAAR_Performance_2016.xlsx
+++ b/data/STAAR_Performance_2016.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11210"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/D/Library/Mobile Documents/com~apple~CloudDocs/R Working Directory/scuc-data-analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/D/Library/Mobile Documents/com~apple~CloudDocs/R Working Directory/scuc-data-analysis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CC79BDE-C571-6A45-938A-CF5812DCD321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DAD982F-C7B7-884A-A348-443E775C515B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1000" windowWidth="27700" windowHeight="16440"/>
+    <workbookView xWindow="2340" yWindow="1000" windowWidth="27700" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="STAAR_Performance_2016" sheetId="1" r:id="rId1"/>
@@ -280,7 +280,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
@@ -1120,14 +1120,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CG16388"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="15.85546875" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="15.42578125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:85" s="1" customFormat="1" ht="40" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:85" s="1" customFormat="1" ht="20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
